--- a/Bangalore-April-2025.xlsx
+++ b/Bangalore-April-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="63">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Bangalore</t>
   </si>
   <si>
@@ -181,10 +184,10 @@
     <t>KA03AK9164</t>
   </si>
   <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>Crysta</t>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
@@ -196,19 +199,19 @@
     <t>BALENO</t>
   </si>
   <si>
-    <t>Toyota Fortuner</t>
-  </si>
-  <si>
-    <t>Maruti Celerio</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>FORTUNER</t>
+  </si>
+  <si>
+    <t>CELERIO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -261,11 +264,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,10 +564,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -642,27 +646,30 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2">
+        <v>56</v>
+      </c>
+      <c r="G2" s="2">
         <v>45055</v>
       </c>
       <c r="H2">
@@ -723,26 +730,26 @@
         <v>9.539999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3">
+        <v>56</v>
+      </c>
+      <c r="G3" s="2">
         <v>44440</v>
       </c>
       <c r="H3">
@@ -803,26 +810,26 @@
         <v>51.12</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4">
+        <v>56</v>
+      </c>
+      <c r="G4" s="2">
         <v>45350</v>
       </c>
       <c r="H4">
@@ -883,26 +890,26 @@
         <v>-36.13</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5">
+        <v>56</v>
+      </c>
+      <c r="G5" s="2">
         <v>45350</v>
       </c>
       <c r="H5">
@@ -963,26 +970,26 @@
         <v>33.92</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
+        <v>56</v>
+      </c>
+      <c r="G6" s="2">
         <v>45350</v>
       </c>
       <c r="H6">
@@ -1043,26 +1050,26 @@
         <v>-11.42</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G7">
+        <v>57</v>
+      </c>
+      <c r="G7" s="2">
         <v>43589</v>
       </c>
       <c r="H7">
@@ -1123,26 +1130,26 @@
         <v>45.98</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8">
+        <v>57</v>
+      </c>
+      <c r="G8" s="2">
         <v>43889</v>
       </c>
       <c r="H8">
@@ -1203,26 +1210,26 @@
         <v>-28.88</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
+        <v>57</v>
+      </c>
+      <c r="G9" s="2">
         <v>44461</v>
       </c>
       <c r="H9">
@@ -1283,26 +1290,26 @@
         <v>55.89</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
+        <v>57</v>
+      </c>
+      <c r="G10" s="2">
         <v>44499</v>
       </c>
       <c r="H10">
@@ -1363,27 +1370,27 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="G11" s="2">
+        <v>44261</v>
       </c>
       <c r="H11">
         <v>71405</v>
@@ -1443,27 +1450,27 @@
         <v>56.72</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="G12" s="2">
+        <v>44461</v>
       </c>
       <c r="H12">
         <v>54717</v>
@@ -1523,26 +1530,26 @@
         <v>55.76</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
+        <v>57</v>
+      </c>
+      <c r="G13" s="2">
         <v>44476</v>
       </c>
       <c r="H13">
@@ -1603,26 +1610,26 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
+        <v>57</v>
+      </c>
+      <c r="G14" s="2">
         <v>44242</v>
       </c>
       <c r="H14">
@@ -1683,26 +1690,26 @@
         <v>-54.97</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
+        <v>57</v>
+      </c>
+      <c r="G15" s="2">
         <v>44230</v>
       </c>
       <c r="H15">
@@ -1763,26 +1770,26 @@
         <v>58.52</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
+        <v>57</v>
+      </c>
+      <c r="G16" s="2">
         <v>44476</v>
       </c>
       <c r="H16">
@@ -1848,22 +1855,22 @@
         <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="G17" s="2">
+        <v>44278</v>
       </c>
       <c r="H17">
         <v>74829</v>
@@ -1928,21 +1935,21 @@
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
+        <v>57</v>
+      </c>
+      <c r="G18" s="2">
         <v>44807</v>
       </c>
       <c r="H18">
@@ -2008,21 +2015,21 @@
         <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19">
+        <v>57</v>
+      </c>
+      <c r="G19" s="2">
         <v>44644</v>
       </c>
       <c r="H19">
@@ -2088,21 +2095,21 @@
         <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20">
+        <v>57</v>
+      </c>
+      <c r="G20" s="2">
         <v>44280</v>
       </c>
       <c r="H20">
@@ -2168,22 +2175,22 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="G21" s="2">
+        <v>44499</v>
       </c>
       <c r="H21">
         <v>45268</v>
@@ -2248,21 +2255,21 @@
         <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
+        <v>58</v>
+      </c>
+      <c r="G22" s="2">
         <v>45008</v>
       </c>
       <c r="H22">
@@ -2328,21 +2335,21 @@
         <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23">
+        <v>58</v>
+      </c>
+      <c r="G23" s="2">
         <v>45016</v>
       </c>
       <c r="H23">
@@ -2408,21 +2415,21 @@
         <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24">
+        <v>58</v>
+      </c>
+      <c r="G24" s="2">
         <v>45016</v>
       </c>
       <c r="H24">
@@ -2488,21 +2495,21 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="G25">
+        <v>59</v>
+      </c>
+      <c r="G25" s="2">
         <v>45055</v>
       </c>
       <c r="H25">
@@ -2568,21 +2575,21 @@
         <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26">
+        <v>60</v>
+      </c>
+      <c r="G26" s="2">
         <v>45057</v>
       </c>
       <c r="H26">
@@ -2648,21 +2655,21 @@
         <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
+        <v>61</v>
+      </c>
+      <c r="G27" s="2">
         <v>44980</v>
       </c>
       <c r="H27">
@@ -2728,21 +2735,21 @@
         <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
-      </c>
-      <c r="G28">
+        <v>62</v>
+      </c>
+      <c r="G28" s="2">
         <v>45055</v>
       </c>
       <c r="H28">
